--- a/tools/config-xlsx/buff.xlsx
+++ b/tools/config-xlsx/buff.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -559,9 +559,73 @@
         <v>debuff</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>taunt_shout</v>
+      </c>
+      <c r="B6" t="str">
+        <v>挑衅</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>refresh</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>taunt</v>
+      </c>
+      <c r="J6" t="str">
+        <v>buff</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>silence_seal</v>
+      </c>
+      <c r="B7" t="str">
+        <v>沉默</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>refresh</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>silence</v>
+      </c>
+      <c r="J7" t="str">
+        <v>debuff</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tools/config-xlsx/buff.xlsx
+++ b/tools/config-xlsx/buff.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -623,9 +623,41 @@
         <v>debuff</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>frost</v>
+      </c>
+      <c r="B8" t="str">
+        <v>冰缓</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
+        <v>refresh</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>moveSpeed%:-0.3</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v>debuff</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tools/config-xlsx/buff.xlsx
+++ b/tools/config-xlsx/buff.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -655,9 +655,41 @@
         <v>debuff</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>war_banner</v>
+      </c>
+      <c r="B9" t="str">
+        <v>战旗</v>
+      </c>
+      <c r="C9">
+        <v>-1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <v>refresh</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>atk%:0.05</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tools/config-xlsx/buff.xlsx
+++ b/tools/config-xlsx/buff.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -687,9 +687,137 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ct_bulwark</v>
+      </c>
+      <c r="B10" t="str">
+        <v>坚韧</v>
+      </c>
+      <c r="C10">
+        <v>-1</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10" t="str">
+        <v>add</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>dmgReduce:+0.01</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ct_shadow</v>
+      </c>
+      <c r="B11" t="str">
+        <v>残影</v>
+      </c>
+      <c r="C11">
+        <v>-1</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" t="str">
+        <v>add</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>dodgeRate:+0.01</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ct_inspire</v>
+      </c>
+      <c r="B12" t="str">
+        <v>鼓舞</v>
+      </c>
+      <c r="C12">
+        <v>-1</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12" t="str">
+        <v>add</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>atk%:0.01</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>ct_po_jun</v>
+      </c>
+      <c r="B13" t="str">
+        <v>破军</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" t="str">
+        <v>add</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>dmgBonus:+0.05</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J13"/>
   </ignoredErrors>
 </worksheet>
 </file>